--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5DFF20-3ADE-4686-A17D-693C4AC1CA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BDF8C7-E947-472D-88AF-AB45FB28C929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t>Petri Laakso (mentorijäsen)</t>
+  </si>
+  <si>
+    <t>Kanban-taulu, tuntiseuranta</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -684,13 +687,24 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BDF8C7-E947-472D-88AF-AB45FB28C929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE9BA42-4535-44D6-AE9D-6D385810BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Kanban-taulu, tuntiseuranta</t>
+  </si>
+  <si>
+    <t>Wireframes</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,13 +701,35 @@
         <v>25</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE9BA42-4535-44D6-AE9D-6D385810BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315A7D90-939C-4E77-B548-6B17A09E15EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Wireframes</t>
+  </si>
+  <si>
+    <t>Nettisivun SEO / GEO</t>
+  </si>
+  <si>
+    <t>Projektin ja viestinnän osuuden raportoinnit</t>
   </si>
 </sst>
 </file>
@@ -173,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -181,6 +187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,7 +555,7 @@
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,6 +611,9 @@
   </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -635,13 +645,35 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>46092</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>46099</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315A7D90-939C-4E77-B548-6B17A09E15EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0ED34B3-9EC6-4454-87D2-AED58E300F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -128,6 +128,12 @@
   </si>
   <si>
     <t>Projektin ja viestinnän osuuden raportoinnit</t>
+  </si>
+  <si>
+    <t>HTML seo/geo opptimointi</t>
+  </si>
+  <si>
+    <t>valokuvien etsiminen nettisivulle</t>
   </si>
 </sst>
 </file>
@@ -184,10 +190,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,28 +521,28 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4"/>
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5"/>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="5"/>
       <c r="C6" t="s">
         <v>17</v>
       </c>
@@ -555,7 +561,7 @@
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -646,7 +652,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46092</v>
       </c>
       <c r="B5">
@@ -657,7 +663,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46099</v>
       </c>
       <c r="B6">
@@ -665,6 +671,28 @@
       </c>
       <c r="C6" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46104</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46105</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -673,7 +701,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE9BA42-4535-44D6-AE9D-6D385810BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759FF84D-5FE3-4B0D-B9BC-2975A573A977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="3795" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13710" yWindow="3900" windowWidth="22605" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -122,6 +122,30 @@
   </si>
   <si>
     <t>Wireframes</t>
+  </si>
+  <si>
+    <t>Nettisivun SEO / GEO</t>
+  </si>
+  <si>
+    <t>Projektin ja viestinnän osuuden raportoinnit</t>
+  </si>
+  <si>
+    <t>HTML seo/geo opptimointi</t>
+  </si>
+  <si>
+    <t>valokuvien etsiminen nettisivulle</t>
+  </si>
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>Kuvien optimointi ja asettelu, sisällön täydennys, muotoiluja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanbanin päivitys, tilannepäivitys projektista, </t>
+  </si>
+  <si>
+    <t>Rakenteen uudelleenjärjestely gridiin, javascript-ominaisuudet, css-siivous ja yhdenmukaistaminen, tiedostohierarkia</t>
   </si>
 </sst>
 </file>
@@ -548,7 +572,7 @@
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -557,7 +581,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,6 +628,9 @@
   </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -635,13 +662,111 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -659,6 +784,9 @@
   </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -723,13 +851,102 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -778,6 +995,72 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
@@ -833,6 +1116,72 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
@@ -888,6 +1237,72 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759FF84D-5FE3-4B0D-B9BC-2975A573A977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D26348-E801-4235-BA07-B9FDCA0CBB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="3900" windowWidth="22605" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13710" yWindow="3900" windowWidth="22605" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>Rakenteen uudelleenjärjestely gridiin, javascript-ominaisuudet, css-siivous ja yhdenmukaistaminen, tiedostohierarkia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -519,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C13"/>
+  <dimension ref="A2:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -609,6 +612,11 @@
       <c r="B13">
         <f>Petri!B27</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zaozerskaya_a/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D26348-E801-4235-BA07-B9FDCA0CBB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BD360F0-6B30-004D-94AD-A98B3DC786C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="3900" windowWidth="22605" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6200" yWindow="2180" windowWidth="22600" windowHeight="15340" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -149,6 +149,27 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">index.html koodaus </t>
+  </si>
+  <si>
+    <t>tilat.html koodaus</t>
+  </si>
+  <si>
+    <t>tapuhtumat.html koodaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jäsenyys.html koodaus </t>
+  </si>
+  <si>
+    <t>form.html koodaus</t>
+  </si>
+  <si>
+    <t>galleria.html koodaus</t>
+  </si>
+  <si>
+    <t>css koodin muutos</t>
   </si>
 </sst>
 </file>
@@ -523,18 +544,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -543,7 +564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -552,7 +573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -561,7 +582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -569,7 +590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -578,7 +599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -587,7 +608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -596,16 +617,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
         <f>Alina!B27</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -614,7 +635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -635,12 +656,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -648,7 +669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -659,7 +680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -670,7 +691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -681,7 +702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -692,7 +713,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -703,7 +724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -714,61 +735,61 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -791,12 +812,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -804,7 +826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -815,7 +837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -826,7 +848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -837,7 +859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -848,7 +870,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -859,7 +881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -870,7 +892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -881,7 +903,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -892,7 +914,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -903,52 +925,52 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -971,9 +993,9 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -981,7 +1003,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -992,7 +1014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1003,73 +1025,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1092,9 +1114,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1102,7 +1127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1113,7 +1138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1124,79 +1149,135 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46103</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>2</v>
+        <v>18.5</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1213,9 +1294,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1223,7 +1304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1234,7 +1315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1245,73 +1326,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zaozerskaya_a/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BD360F0-6B30-004D-94AD-A98B3DC786C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B925A18-29D6-449B-99FA-1CAB162512CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6200" yWindow="2180" windowWidth="22600" windowHeight="15340" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="5640" windowWidth="20430" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>css koodin muutos</t>
+  </si>
+  <si>
+    <t>Palautuspiste 2 raportti</t>
   </si>
 </sst>
 </file>
@@ -544,18 +547,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -564,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -573,7 +576,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -582,7 +585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -590,7 +593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -599,16 +602,16 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -617,7 +620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -626,7 +629,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -635,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -656,12 +659,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -669,7 +672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -680,7 +683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -691,7 +694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -702,7 +705,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -713,7 +716,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -724,7 +727,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -735,61 +738,61 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -812,13 +815,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -826,7 +829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -837,7 +840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -848,7 +851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -859,7 +862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -870,7 +873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -881,7 +884,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -892,7 +895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -903,7 +906,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -914,7 +917,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -925,58 +928,66 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -993,9 +1004,9 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1003,7 +1014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1014,7 +1025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1025,73 +1036,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1114,12 +1125,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1138,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1149,7 +1160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46101</v>
       </c>
@@ -1160,7 +1171,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46102</v>
       </c>
@@ -1171,7 +1182,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46103</v>
       </c>
@@ -1182,7 +1193,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46104</v>
       </c>
@@ -1193,7 +1204,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46104</v>
       </c>
@@ -1204,7 +1215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46105</v>
       </c>
@@ -1215,7 +1226,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46105</v>
       </c>
@@ -1226,52 +1237,52 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1294,9 +1305,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1304,7 +1315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1315,7 +1326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1326,73 +1337,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B925A18-29D6-449B-99FA-1CAB162512CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{828CE175-CA7C-084B-83AF-75C48EA48074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="5640" windowWidth="20430" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="1140" windowWidth="20440" windowHeight="15240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Matias Luoma-aho</t>
   </si>
   <si>
-    <t>Olga Popova</t>
-  </si>
-  <si>
     <t>Jäsen 5:</t>
   </si>
   <si>
@@ -173,6 +170,21 @@
   </si>
   <si>
     <t>Palautuspiste 2 raportti</t>
+  </si>
+  <si>
+    <t>Rakenteen koodaus</t>
+  </si>
+  <si>
+    <t>Rakenteen  koodaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen koodaus css:iin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen esite sunnittelu </t>
+  </si>
+  <si>
+    <t>Tyylijen css luonnos koodaus</t>
   </si>
 </sst>
 </file>
@@ -547,18 +559,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -567,7 +579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -576,7 +588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -585,7 +597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -593,7 +605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -602,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -611,16 +623,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <f>Olga!B27</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Olga!B26</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -629,7 +641,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -638,9 +650,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -659,12 +671,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -672,7 +684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -683,7 +695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -694,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -702,10 +714,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -713,10 +725,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -724,10 +736,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -735,64 +747,64 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -815,13 +827,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -829,7 +841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -840,7 +852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -851,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -859,10 +871,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -870,10 +882,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -881,10 +893,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -892,10 +904,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -903,10 +915,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -914,10 +926,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -925,10 +937,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>46112</v>
       </c>
@@ -936,52 +948,52 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1003,18 +1015,21 @@
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1025,7 +1040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1036,81 +1051,134 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46115</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B10">
+        <v>3.5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B11">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="B27">
-        <f>SUM(B4:B26)</f>
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B26">
+        <f>SUM(B4:B25)</f>
+        <v>17.5</v>
+      </c>
+      <c r="C26" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1125,12 +1193,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1138,7 +1206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1149,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1160,7 +1228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46101</v>
       </c>
@@ -1168,10 +1236,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46102</v>
       </c>
@@ -1179,10 +1247,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46103</v>
       </c>
@@ -1190,10 +1258,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46104</v>
       </c>
@@ -1201,10 +1269,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46104</v>
       </c>
@@ -1212,10 +1280,10 @@
         <v>1.5</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46105</v>
       </c>
@@ -1223,10 +1291,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46105</v>
       </c>
@@ -1234,55 +1302,55 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1305,17 +1373,17 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1326,7 +1394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1337,73 +1405,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D26348-E801-4235-BA07-B9FDCA0CBB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{828CE175-CA7C-084B-83AF-75C48EA48074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="3900" windowWidth="22605" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="1140" windowWidth="20440" windowHeight="15240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Matias Luoma-aho</t>
   </si>
   <si>
-    <t>Olga Popova</t>
-  </si>
-  <si>
     <t>Jäsen 5:</t>
   </si>
   <si>
@@ -149,6 +146,45 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">index.html koodaus </t>
+  </si>
+  <si>
+    <t>tilat.html koodaus</t>
+  </si>
+  <si>
+    <t>tapuhtumat.html koodaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jäsenyys.html koodaus </t>
+  </si>
+  <si>
+    <t>form.html koodaus</t>
+  </si>
+  <si>
+    <t>galleria.html koodaus</t>
+  </si>
+  <si>
+    <t>css koodin muutos</t>
+  </si>
+  <si>
+    <t>Palautuspiste 2 raportti</t>
+  </si>
+  <si>
+    <t>Rakenteen koodaus</t>
+  </si>
+  <si>
+    <t>Rakenteen  koodaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen koodaus css:iin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen esite sunnittelu </t>
+  </si>
+  <si>
+    <t>Tyylijen css luonnos koodaus</t>
   </si>
 </sst>
 </file>
@@ -523,18 +559,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -543,7 +579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -552,7 +588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -561,7 +597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -569,7 +605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -578,34 +614,34 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <f>Olga!B27</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Olga!B26</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
         <f>Alina!B27</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -614,9 +650,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -635,12 +671,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -648,7 +684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -659,7 +695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -670,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -678,10 +714,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -689,10 +725,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -700,10 +736,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -711,64 +747,64 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -791,12 +827,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -804,7 +841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -815,7 +852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -826,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -834,10 +871,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -845,10 +882,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -856,10 +893,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -867,10 +904,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -878,10 +915,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -889,10 +926,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -900,61 +937,69 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -970,18 +1015,21 @@
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -992,7 +1040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1003,81 +1051,134 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46115</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B10">
+        <v>3.5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B11">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="B27">
-        <f>SUM(B4:B26)</f>
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B26">
+        <f>SUM(B4:B25)</f>
+        <v>17.5</v>
+      </c>
+      <c r="C26" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1092,9 +1193,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1102,7 +1206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1113,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1124,79 +1228,135 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46103</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>2</v>
+        <v>18.5</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1213,17 +1373,17 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1234,7 +1394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1245,73 +1405,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{828CE175-CA7C-084B-83AF-75C48EA48074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6972F27C-019D-491C-80FF-D5586A1FB116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="1140" windowWidth="20440" windowHeight="15240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Tyylijen css luonnos koodaus</t>
+  </si>
+  <si>
+    <t>Nettisivun viimeistelyä</t>
   </si>
 </sst>
 </file>
@@ -559,18 +562,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -579,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -588,7 +591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -597,7 +600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -605,16 +608,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -623,7 +626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -632,7 +635,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -641,7 +644,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -650,7 +653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -671,12 +674,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -684,7 +687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -695,7 +698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -706,7 +709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -717,7 +720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -728,7 +731,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -739,7 +742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -750,67 +753,75 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -827,13 +838,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -841,7 +852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -852,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -863,7 +874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -874,7 +885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -885,7 +896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -896,7 +907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -907,7 +918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -918,7 +929,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -929,7 +940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -940,7 +951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46112</v>
       </c>
@@ -951,49 +962,49 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1016,12 +1027,12 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1029,7 +1040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1040,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1051,7 +1062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46093</v>
       </c>
@@ -1062,7 +1073,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46095</v>
       </c>
@@ -1073,7 +1084,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -1084,7 +1095,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46136</v>
       </c>
@@ -1095,7 +1106,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46115</v>
       </c>
@@ -1106,7 +1117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46126</v>
       </c>
@@ -1117,7 +1128,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46126</v>
       </c>
@@ -1128,49 +1139,49 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1193,12 +1204,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1206,7 +1217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1217,7 +1228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1228,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46101</v>
       </c>
@@ -1239,7 +1250,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46102</v>
       </c>
@@ -1250,7 +1261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46103</v>
       </c>
@@ -1261,7 +1272,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46104</v>
       </c>
@@ -1272,7 +1283,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46104</v>
       </c>
@@ -1283,7 +1294,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46105</v>
       </c>
@@ -1294,7 +1305,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46105</v>
       </c>
@@ -1305,52 +1316,52 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1373,9 +1384,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1383,7 +1394,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1405,73 +1416,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6972F27C-019D-491C-80FF-D5586A1FB116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB00B89C-308E-48FD-9191-B50AB6CEA4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="4890" windowWidth="20430" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>Nettisivun viimeistelyä</t>
+  </si>
+  <si>
+    <t>Vertaispalautteen käsittely, raportin kirjoittamista useana eri päivänä, projektinhallintaa</t>
   </si>
 </sst>
 </file>
@@ -623,7 +626,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -963,7 +966,15 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -1010,7 +1021,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB00B89C-308E-48FD-9191-B50AB6CEA4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{828CE175-CA7C-084B-83AF-75C48EA48074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="4890" windowWidth="20430" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="1140" windowWidth="20440" windowHeight="15240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -185,12 +185,6 @@
   </si>
   <si>
     <t>Tyylijen css luonnos koodaus</t>
-  </si>
-  <si>
-    <t>Nettisivun viimeistelyä</t>
-  </si>
-  <si>
-    <t>Vertaispalautteen käsittely, raportin kirjoittamista useana eri päivänä, projektinhallintaa</t>
   </si>
 </sst>
 </file>
@@ -565,18 +559,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -585,7 +579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -594,7 +588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -603,7 +597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -611,25 +605,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -638,7 +632,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -647,7 +641,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -656,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -677,12 +671,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -690,7 +684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -701,7 +695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -712,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -723,7 +717,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -734,7 +728,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -745,7 +739,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -756,75 +750,67 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -841,13 +827,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -855,7 +841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -866,7 +852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -877,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -888,7 +874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -899,7 +885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -910,7 +896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -921,7 +907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -932,7 +918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -943,7 +929,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -954,7 +940,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>46112</v>
       </c>
@@ -965,63 +951,55 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1038,12 +1016,12 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1051,7 +1029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1062,7 +1040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1073,7 +1051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46093</v>
       </c>
@@ -1084,7 +1062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46095</v>
       </c>
@@ -1095,7 +1073,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -1106,7 +1084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46136</v>
       </c>
@@ -1117,7 +1095,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46115</v>
       </c>
@@ -1128,7 +1106,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46126</v>
       </c>
@@ -1139,7 +1117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46126</v>
       </c>
@@ -1150,49 +1128,49 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1215,12 +1193,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1228,7 +1206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1239,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1250,7 +1228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46101</v>
       </c>
@@ -1261,7 +1239,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46102</v>
       </c>
@@ -1272,7 +1250,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46103</v>
       </c>
@@ -1283,7 +1261,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46104</v>
       </c>
@@ -1294,7 +1272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46104</v>
       </c>
@@ -1305,7 +1283,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46105</v>
       </c>
@@ -1316,7 +1294,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46105</v>
       </c>
@@ -1327,52 +1305,52 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1395,9 +1373,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1405,7 +1383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1416,7 +1394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1427,73 +1405,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{828CE175-CA7C-084B-83AF-75C48EA48074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CECCAD-32AF-834B-8EBD-D7B37BE48596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="1140" windowWidth="20440" windowHeight="15240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="1140" windowWidth="20440" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -181,10 +181,22 @@
     <t xml:space="preserve">Tyyliohjen koodaus css:iin </t>
   </si>
   <si>
-    <t xml:space="preserve">Tyyliohjen esite sunnittelu </t>
-  </si>
-  <si>
     <t>Tyylijen css luonnos koodaus</t>
+  </si>
+  <si>
+    <t>Nettisivun viimeistelyä</t>
+  </si>
+  <si>
+    <t>Vertaispalautteen käsittely, raportin kirjoittamista useana eri päivänä, projektinhallintaa</t>
+  </si>
+  <si>
+    <t>Korjaukset vertaiarvionnin mukaan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen esitteen sunnittelu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyyliohjen esittene sunnittelu </t>
   </si>
 </sst>
 </file>
@@ -611,7 +623,7 @@
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -620,7 +632,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -629,7 +641,7 @@
       </c>
       <c r="B11">
         <f>Olga!B26</f>
-        <v>17.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -638,7 +650,7 @@
       </c>
       <c r="B12">
         <f>Alina!B27</f>
-        <v>18.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -751,7 +763,15 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -810,7 +830,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -952,7 +972,15 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
@@ -999,7 +1027,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1081,7 +1109,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,7 +1120,7 @@
         <v>1.5</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1125,14 +1153,30 @@
         <v>2.5</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
@@ -1176,7 +1220,7 @@
       </c>
       <c r="B26">
         <f>SUM(B4:B25)</f>
-        <v>17.5</v>
+        <v>21.5</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1306,7 +1350,15 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
@@ -1356,7 +1408,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>18.5</v>
+        <v>21.5</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olga/Desktop/UNI/prpjekti_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F197E14-A746-CB4A-AD4B-1D453A3603B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B21475-3565-459F-97EC-11D02EF5B5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="1140" windowWidth="20440" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t xml:space="preserve">Tyyliohjen esittene sunnittelu </t>
+  </si>
+  <si>
+    <t>Ryhmä 14 palaute</t>
+  </si>
+  <si>
+    <t>Posterin tekoa</t>
   </si>
 </sst>
 </file>
@@ -571,18 +577,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -591,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -600,7 +606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -609,7 +615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -617,16 +623,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
         <f>Matias!B27</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -635,7 +641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -644,7 +650,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -653,7 +659,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -662,7 +668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -683,12 +689,12 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -696,7 +702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -707,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -718,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46092</v>
       </c>
@@ -729,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46099</v>
       </c>
@@ -740,7 +746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -751,7 +757,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -762,7 +768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46131</v>
       </c>
@@ -773,64 +779,80 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -847,13 +869,13 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -861,7 +883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -872,7 +894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -883,7 +905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46085</v>
       </c>
@@ -894,7 +916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46085</v>
       </c>
@@ -905,7 +927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46087</v>
       </c>
@@ -916,7 +938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46105</v>
       </c>
@@ -927,7 +949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46106</v>
       </c>
@@ -938,7 +960,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46107</v>
       </c>
@@ -949,7 +971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46107</v>
       </c>
@@ -960,7 +982,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46112</v>
       </c>
@@ -971,7 +993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46130</v>
       </c>
@@ -982,46 +1004,46 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1044,12 +1066,12 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1057,7 +1079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1068,7 +1090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1079,7 +1101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46093</v>
       </c>
@@ -1090,7 +1112,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46095</v>
       </c>
@@ -1101,7 +1123,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46104</v>
       </c>
@@ -1112,7 +1134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46136</v>
       </c>
@@ -1123,7 +1145,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46115</v>
       </c>
@@ -1134,7 +1156,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46126</v>
       </c>
@@ -1145,7 +1167,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46126</v>
       </c>
@@ -1156,7 +1178,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46131</v>
       </c>
@@ -1167,7 +1189,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46132</v>
       </c>
@@ -1178,43 +1200,43 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1237,12 +1259,12 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1250,7 +1272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1261,7 +1283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1272,7 +1294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46101</v>
       </c>
@@ -1283,7 +1305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46102</v>
       </c>
@@ -1294,7 +1316,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46103</v>
       </c>
@@ -1305,7 +1327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46104</v>
       </c>
@@ -1316,7 +1338,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46104</v>
       </c>
@@ -1327,7 +1349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46105</v>
       </c>
@@ -1338,7 +1360,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46105</v>
       </c>
@@ -1349,7 +1371,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46131</v>
       </c>
@@ -1360,49 +1382,49 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1425,9 +1447,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1435,7 +1457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1446,7 +1468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46085</v>
       </c>
@@ -1457,73 +1479,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>

--- a/Muut/Tuntikirjanpito.xlsx
+++ b/Muut/Tuntikirjanpito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taika\Documents\GitHub\Tuoteprojekti1\Muut\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B21475-3565-459F-97EC-11D02EF5B5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2560E42D-19A2-45EF-82E4-4223BF3331C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="4890" windowWidth="20430" windowHeight="15240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YHTEENVETO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>TUNTIKIRJANPITO, TUOTEKEHITYSPROJEKTI I</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>Posterin tekoa</t>
+  </si>
+  <si>
+    <t>Raportin viimeistely</t>
   </si>
 </sst>
 </file>
@@ -638,7 +641,7 @@
       </c>
       <c r="B10">
         <f>Ilona!B27</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1005,7 +1008,15 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
@@ -1049,7 +1060,7 @@
       </c>
       <c r="B27">
         <f>SUM(B4:B26)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
